--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:12</t>
+    <t xml:space="preserve">2026-09-09 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:47</t>
+    <t xml:space="preserve">2026-09-17 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:10</t>
+    <t xml:space="preserve">2026-09-27 02:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:40</t>
+    <t xml:space="preserve">2026-10-03 02:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 02:03</t>
+    <t xml:space="preserve">2026-10-05 05:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
